--- a/demo/Baseline-demo.xlsx
+++ b/demo/Baseline-demo.xlsx
@@ -73,15 +73,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
@@ -450,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="95" customWidth="1" min="1" max="1"/>
@@ -483,7 +488,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3. Expand a red item and click a cell link, e.g. B10, to jump to it.</t>
+          <t>3. Expand a red item and click a cell link, e.g. C14, to jump to it.</t>
         </is>
       </c>
     </row>
@@ -504,38 +509,52 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5. Fix something live: change FY25 Cash B10 to =SUM(B6:B9) and watch it turn green.</t>
+          <t xml:space="preserve">   Notes Baseline can't test automatically show as "Check yourself".</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Also try B13 → =B12*B14 (links the FX rate) and add 'Reviewed by:' in A4.</t>
+          <t>5. Fix something live: change FY25 Cash C14 to =SUM(C10:C13) and watch it turn green.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6. Try "FY25 AR": a typed-over formula, an inconsistent formula and a #DIV/0!.</t>
+          <t xml:space="preserve">   Also try C21 → =C19*C20 (links the FX rate), then add a Reviewed by: line in A4,</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t xml:space="preserve">   a Source: line in A5 and a Tickmark legend: line in A6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>6. Try "FY25 AR": a typed-over total (F10), an inconsistent formula (G9) and a #DIV/0!.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>7. "FY25 Fixed Assets" is a clean sheet that passes every check.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>All figures are made up. Nothing in this file leaves Excel.</t>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>The client and all figures are made up. Nothing in this file leaves Excel.</t>
         </is>
       </c>
     </row>
@@ -550,152 +569,325 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Cash: bank reconciliation, 31 Dec 2025</t>
+          <t>Prairie Ridge Mining Ltd. · WP 4.1 Cash: bank reconciliation, 31 Dec 2025</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Purpose: reconcile the operating account balance to the bank statement</t>
+          <t>Purpose: reconcile GL cash (acct 1010) to the bank and test the reconciling items</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Prepared by: JS 06/10/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+          <t>Prepared by: JS 14 Jan 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Amount</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Tick</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Balance per bank statement</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>482150</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Deposits in transit</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>36400</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>✓</t>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Comment</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Outstanding cheques</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>-51275</v>
-      </c>
-      <c r="C8" t="inlineStr">
+          <t>Balance per bank statement</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BS-1</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>1284610</v>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>✓</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Agreed to statement p.3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bank error correction</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>1200</v>
+          <t>Add: deposits in transit</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>DIT-1</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>86420</v>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2 deposits; cleared 2 Jan 2026</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Adjusted bank balance</t>
-        </is>
-      </c>
-      <c r="B10" s="6">
-        <f>SUM(B6:B8)</f>
-        <v/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Less: chq 10442 · Pioneer Drilling</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" s="4" t="n">
+        <v>-41300</v>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Outstanding at 31 Dec 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Less: chq 10447 · Cobalt Freight</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" s="4" t="n">
+        <v>-18950</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Outstanding at 31 Dec 2025</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>USD sub-account (USD)</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>25000</v>
+          <t>Less: chq 10451 · Wascana Safety</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" s="4" t="n">
+        <v>-22775</v>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Outstanding at 31 Dec 2025</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Less: chq 10455 · SaskPower</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" s="4" t="n">
+        <v>-9420</v>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Outstanding at 31 Dec 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Total outstanding cheques</t>
+        </is>
+      </c>
+      <c r="C14" s="7">
+        <f>SUM(C10:C12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Add: bank error (fee charged in error)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>BE-1</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>3200</v>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Reversed by bank 3 Jan 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Adjusted bank balance</t>
+        </is>
+      </c>
+      <c r="C16" s="7">
+        <f>C8+C9+C14+C15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Balance per GL (acct 1010)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>1281785</v>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Agreed to trial balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Difference</t>
+        </is>
+      </c>
+      <c r="C18" s="7">
+        <f>C16-C17</f>
+        <v/>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Should be nil</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>USD sub-account (USD)</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>58300</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>FX rate USD→CAD</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>per Bank of Canada 31 Dec close</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>USD sub-account (CAD)</t>
         </is>
       </c>
-      <c r="B13" s="4">
-        <f>B12*1.37</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>FX rate USD→CAD</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>per Bank of Canada 31 Dec close</t>
-        </is>
+      <c r="C21" s="4">
+        <f>C19*1.37</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -709,45 +901,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Accounts receivable: aging, 31 Dec 2025</t>
+          <t>Prairie Ridge Mining Ltd. · WP 5.2 Trade receivables: aging and ECL allowance, 31 Dec 2025</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Purpose: test the AR aging and allowance</t>
+          <t>Purpose: test the aging for accuracy and recalculate the expected credit loss (ECL) allowance</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Source: AR aging report from the client's system, 3 Jan 2026</t>
+          <t>Source: AR aging report run 3 Jan 2026 (client system); control account GL 1200</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Prepared by: JS 06/10/2025</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+          <t>Prepared by: JS 15 Jan 2026</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>Reviewed by:</t>
         </is>
@@ -761,7 +954,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>0-30</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -776,10 +969,15 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
+          <t>90+</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>% of total</t>
         </is>
@@ -788,161 +986,335 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Northwind Traders</t>
+          <t>Northern Reach Energy</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>18200</v>
+        <v>212400</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4100</v>
+        <v>38200</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>900</v>
-      </c>
-      <c r="E7" s="4">
-        <f>SUM(B7:D7)</f>
-        <v/>
-      </c>
-      <c r="F7" s="7">
-        <f>E7/$E$12</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="8">
+        <f>SUM(B7:E7)</f>
+        <v/>
+      </c>
+      <c r="G7" s="9">
+        <f>F7/F$15</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Contoso Ltd</t>
+          <t>Boreal Haulage Ltd.</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>22750</v>
+        <v>96750</v>
       </c>
       <c r="C8" s="4" t="n">
+        <v>41300</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>12900</v>
+      </c>
+      <c r="E8" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="4" t="n">
-        <v>3300</v>
-      </c>
-      <c r="E8" s="4">
-        <f>SUM(B8:D8)</f>
-        <v/>
-      </c>
-      <c r="F8" s="7">
-        <f>E8/$E$12</f>
+      <c r="F8" s="8">
+        <f>SUM(B8:E8)</f>
+        <v/>
+      </c>
+      <c r="G8" s="9">
+        <f>F8/F$15</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Fabrikam Inc</t>
+          <t>Lakeshore Fabricators</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>9800</v>
+        <v>54300</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>2250</v>
+        <v>22100</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0</v>
+        <v>31800</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>14050</v>
-      </c>
-      <c r="F9" s="7">
-        <f>E9/$E$12</f>
+        <v>48600</v>
+      </c>
+      <c r="F9" s="8">
+        <f>SUM(B9:E9)</f>
+        <v/>
+      </c>
+      <c r="G9" s="9">
+        <f>F9/F16</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Adventure Works</t>
+          <t>Prairie Steel Works</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>14100</v>
+        <v>143900</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>6400</v>
+        <v>27450</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1750</v>
-      </c>
-      <c r="E10" s="4">
-        <f>SUM(B10:D10)</f>
-        <v/>
-      </c>
-      <c r="F10" s="7">
-        <f>E10/$E$13</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>168850</v>
+      </c>
+      <c r="G10" s="9">
+        <f>F10/F$15</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Tailspin Toys</t>
+          <t>Wascana Industrial Supply</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>7300</v>
+        <v>38200</v>
       </c>
       <c r="C11" s="4" t="n">
+        <v>9800</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>6350</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>2150</v>
+      </c>
+      <c r="F11" s="8">
+        <f>SUM(B11:E11)</f>
+        <v/>
+      </c>
+      <c r="G11" s="9">
+        <f>F11/F$15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Meridian Pipe &amp; Fittings</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>77600</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D12" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="E12" s="4" t="n">
+        <v>11200</v>
+      </c>
+      <c r="F12" s="8">
+        <f>SUM(B12:E12)</f>
+        <v/>
+      </c>
+      <c r="G12" s="9">
+        <f>F12/F$15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Tallgrass Environmental</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>28950</v>
+      </c>
+      <c r="C13" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="4">
-        <f>SUM(B11:D11)</f>
-        <v/>
-      </c>
-      <c r="F11" s="7">
-        <f>E11/$E$12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="D13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="8">
+        <f>SUM(B13:E13)</f>
+        <v/>
+      </c>
+      <c r="G13" s="9">
+        <f>F13/F$15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Kestrel Drilling Services</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>64100</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>18900</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>7700</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="8">
+        <f>SUM(B14:E14)</f>
+        <v/>
+      </c>
+      <c r="G14" s="9">
+        <f>F14/F$15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="6">
-        <f>SUM(B7:B11)</f>
-        <v/>
-      </c>
-      <c r="C12" s="6">
-        <f>SUM(C7:C11)</f>
-        <v/>
-      </c>
-      <c r="D12" s="6">
-        <f>SUM(D7:D11)</f>
-        <v/>
-      </c>
-      <c r="E12" s="6">
-        <f>SUM(E7:E11)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Allowance coverage</t>
-        </is>
-      </c>
-      <c r="B15">
-        <f>E12/B16</f>
+      <c r="B15" s="7">
+        <f>SUM(B7:B14)</f>
+        <v/>
+      </c>
+      <c r="C15" s="7">
+        <f>SUM(C7:C14)</f>
+        <v/>
+      </c>
+      <c r="D15" s="7">
+        <f>SUM(D7:D14)</f>
+        <v/>
+      </c>
+      <c r="E15" s="7">
+        <f>SUM(E7:E14)</f>
+        <v/>
+      </c>
+      <c r="F15" s="7">
+        <f>SUM(F7:F14)</f>
+        <v/>
+      </c>
+      <c r="G15" s="10">
+        <f>SUM(G7:G14)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Allowance for doubtful accounts</t>
-        </is>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>ECL rate (policy matrix)</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Collective ECL by bucket</t>
+        </is>
+      </c>
+      <c r="B17" s="4">
+        <f>B15*B16</f>
+        <v/>
+      </c>
+      <c r="C17" s="4">
+        <f>C15*C16</f>
+        <v/>
+      </c>
+      <c r="D17" s="4">
+        <f>D15*D16</f>
+        <v/>
+      </c>
+      <c r="E17" s="4">
+        <f>E15*E16</f>
+        <v/>
+      </c>
+      <c r="F17" s="8">
+        <f>SUM(B17:E17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Specific provision · Lakeshore (disputed invoice)</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Required allowance</t>
+        </is>
+      </c>
+      <c r="F19" s="7">
+        <f>F17+F18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Allowance booked per GL (1205)</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>54000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Difference</t>
+        </is>
+      </c>
+      <c r="F21" s="7">
+        <f>F19-F20</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -956,129 +1328,140 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Fixed assets: additions and depreciation, FY2025</t>
+          <t>Prairie Ridge Mining Ltd. · WP 7.1 PP&amp;E: FY2025 additions and depreciation recalculation</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Purpose: recalculate straight-line depreciation on FY25 additions</t>
+          <t>Purpose: vouch FY2025 additions and recalculate straight-line depreciation</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Source: fixed asset register export, 2 Jan 2026</t>
+          <t>Source: fixed asset register export 2 Jan 2026; vendor invoices (sample of 5)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Prepared by: JS 06/10/2025</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+          <t>Prepared by: JS 16 Jan 2026</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>Reviewed by:</t>
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Tickmark legend: ✓ agreed to vendor invoice, approved capex and in-service date</t>
+        </is>
+      </c>
+    </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Months in period (year ended 31 Dec 2025)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Asset (FY2025 addition)</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Cost</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Useful life (yrs)</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Life (yrs)</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>In service</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Months</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>Depreciation</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>Net book value</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>Tick</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Delivery van</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>48000</v>
-      </c>
-      <c r="C7" t="n">
-        <v>6</v>
-      </c>
-      <c r="D7" s="4">
-        <f>B7/C7</f>
-        <v/>
-      </c>
-      <c r="E7" s="4">
-        <f>B7-D7</f>
-        <v/>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Laptops (12)</t>
+          <t>Haul truck · CAT 777</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>21600</v>
+        <v>1480000</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
-      </c>
-      <c r="D8" s="4">
-        <f>B8/C8</f>
-        <v/>
-      </c>
-      <c r="E8" s="4">
-        <f>B8-D8</f>
-        <v/>
-      </c>
-      <c r="F8" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1 Mar 2025</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" s="4">
+        <f>B8/C8*E8/$B$6</f>
+        <v/>
+      </c>
+      <c r="G8" s="4">
+        <f>B8-F8</f>
+        <v/>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -1087,24 +1470,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Warehouse racking</t>
+          <t>Crusher liner set</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>35500</v>
+        <v>312500</v>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
-      </c>
-      <c r="D9" s="4">
-        <f>B9/C9</f>
-        <v/>
-      </c>
-      <c r="E9" s="4">
-        <f>B9-D9</f>
-        <v/>
-      </c>
-      <c r="F9" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1 Jun 2025</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>7</v>
+      </c>
+      <c r="F9" s="4">
+        <f>B9/C9*E9/$B$6</f>
+        <v/>
+      </c>
+      <c r="G9" s="4">
+        <f>B9-F9</f>
+        <v/>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -1113,60 +1504,197 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Forklift</t>
+          <t>Survey drone &amp; GNSS</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>29900</v>
+        <v>48900</v>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
-      </c>
-      <c r="D10" s="4">
-        <f>B10/C10</f>
-        <v/>
-      </c>
-      <c r="E10" s="4">
-        <f>B10-D10</f>
-        <v/>
-      </c>
-      <c r="F10" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1 Aug 2025</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" s="4">
+        <f>B10/C10*E10/$B$6</f>
+        <v/>
+      </c>
+      <c r="G10" s="4">
+        <f>B10-F10</f>
+        <v/>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B11" s="6">
-        <f>SUM(B7:B10)</f>
-        <v/>
-      </c>
-      <c r="D11" s="6">
-        <f>SUM(D7:D10)</f>
-        <v/>
-      </c>
-      <c r="E11" s="6">
-        <f>SUM(E7:E10)</f>
-        <v/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Site office module</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>215000</v>
+      </c>
+      <c r="C11" t="n">
+        <v>15</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1 Jul 2025</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6</v>
+      </c>
+      <c r="F11" s="4">
+        <f>B11/C11*E11/$B$6</f>
+        <v/>
+      </c>
+      <c r="G11" s="4">
+        <f>B11-F11</f>
+        <v/>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Water treatment skid</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>640000</v>
+      </c>
+      <c r="C12" t="n">
+        <v>12</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1 Oct 2025</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" s="4">
+        <f>B12/C12*E12/$B$6</f>
+        <v/>
+      </c>
+      <c r="G12" s="4">
+        <f>B12-F12</f>
+        <v/>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Tickmark legend</t>
-        </is>
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Total additions</t>
+        </is>
+      </c>
+      <c r="B13" s="7">
+        <f>SUM(B8:B12)</f>
+        <v/>
+      </c>
+      <c r="F13" s="7">
+        <f>SUM(F8:F12)</f>
+        <v/>
+      </c>
+      <c r="G13" s="7">
+        <f>SUM(G8:G12)</f>
+        <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>✓ = agreed cost to invoice and useful life to policy</t>
-        </is>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Cost rollforward</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Opening cost per prior-year WP 7.1</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>18420000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Additions (above)</t>
+        </is>
+      </c>
+      <c r="B16" s="4">
+        <f>B13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Disposals (WP 7.3)</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>-225000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Closing cost</t>
+        </is>
+      </c>
+      <c r="B18" s="7">
+        <f>SUM(B15:B17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Closing cost per GL (acct 1500)</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>20891400</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Difference</t>
+        </is>
+      </c>
+      <c r="B20" s="7">
+        <f>B18-B19</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1180,7 +1708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1213,12 +1741,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>B10</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>Total doesn't foot: adjusted balance excludes the last reconciling item</t>
+          <t>C13</t>
+        </is>
+      </c>
+      <c r="C2" s="11" t="inlineStr">
+        <is>
+          <t>Outstanding cheques total doesn't foot: the last cheque listed is excluded from the sum range</t>
         </is>
       </c>
     </row>
@@ -1230,12 +1758,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>B13</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>Hard-coded FX rate, link to source</t>
+          <t>C20</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>FX rate hard-coded in the formula; link to the Bank of Canada rate and cite it</t>
         </is>
       </c>
     </row>
@@ -1245,70 +1773,180 @@
           <t>FY24 Cash</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>Please sign off and add the reviewer line</t>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>Source not documented: cite the bank statement and its date</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FY24 AR</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>E9</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>Formula overwritten with a typed number, re-link the total</t>
+          <t>FY24 Cash</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Please sign off and add the reviewer line</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FY24 AR</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>Discuss allowance methodology with manager</t>
+          <t>FY24 Cash</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>Cheques outstanding over 90 days: assess whether stale-dated and whether to reverse</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FY24 Fixed Assets</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Where is the tickmark legend?</t>
+          <t>FY24 Cash</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>Deposits in transit: agree to January bank activity and document clearing dates</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>FY24 AR</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>F9</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>Customer total overwritten with a typed number; re-link the total</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>FY24 AR</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>G8</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>% of total formula is inconsistent: one row points at the wrong total</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FY24 AR</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>E16</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>Support the 35% rate for the 90+ bucket against historic write-offs</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>FY24 AR</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>F18</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>Lakeshore: obtain management or legal support for the specific provision</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>FY24 Fixed Assets</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>D8</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Hard-coded useful life in depreciation formula</t>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>E8</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Useful life hard-coded in the depreciation formula; link to the life column</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>FY24 Fixed Assets</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>A13</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Where is the tickmark legend?</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>FY24 Fixed Assets</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>B8</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>Confirm additions meet the capitalization threshold and note who approved the capex</t>
         </is>
       </c>
     </row>

--- a/demo/Baseline-demo.xlsx
+++ b/demo/Baseline-demo.xlsx
@@ -11,7 +11,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FY25 Cash" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FY25 AR" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FY25 Fixed Assets" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PY Notes" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FY25 SURL" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FY25 Revenue cut-off" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FY25 AR confirmations" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PY Notes" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,9 +23,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="#,##0;(#,##0)"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="166" formatCode="dd-mmm-yy"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -73,7 +78,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -81,7 +86,8 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
@@ -450,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="95" customWidth="1" min="1" max="1"/>
@@ -476,64 +482,78 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2. Click the "FY25 Cash" tab. The checklist shows 5 problems.</t>
+          <t>2. Settings tab: set year-end to 31 Dec 2025 (or click 'Use it') and threshold to 10000. Save.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3. Expand a red item and click a cell link, e.g. B10, to jump to it.</t>
+          <t>3. Click the "FY25 Cash" tab. Baseline suggests the Bank reconciliation reviewer. Click "Use it".</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4. Open "Last year's notes" in the add-in → Import from "PY Notes" sheet.</t>
+          <t xml:space="preserve">   Insights show the rec is $1,200 off the GL, a stale cheque, one that cleared before year-end, and more.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Back on Review, the yellow box shows which of last year's notes are happening again.</t>
+          <t>4. Expand a red item and click a cell link, e.g. B10, to jump to it.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5. Fix something live: change FY25 Cash B10 to =SUM(B6:B9) and watch it turn green.</t>
+          <t>5. PY notes tab → Import from "PY Notes" sheet. The yellow box shows last year's issues happening again.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Also try B13 → =B12*B14 (links the FX rate) and add 'Reviewed by:' in A4.</t>
+          <t>6. Fix something live: change FY25 Cash B10 to =SUM(B6:B9). The total and the GL difference both clear.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6. Try "FY25 AR": a typed-over formula, an inconsistent formula and a #DIV/0!.</t>
+          <t>7. Open the Catalog tab to see every reviewer. Try "FY25 SURL", "FY25 Revenue cut-off" and</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>7. "FY25 Fixed Assets" is a clean sheet that passes every check.</t>
+          <t xml:space="preserve">   "FY25 AR confirmations": each gets its own suggestion, checklist and high-risk items.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>8. "FY25 AR" has a typed-over formula, an inconsistent formula and #DIV/0! errors.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>9. "FY25 Fixed Assets" is a clean sheet that passes every check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>All figures are made up. Nothing in this file leaves Excel.</t>
         </is>
@@ -550,12 +570,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -662,6 +685,16 @@
         <v/>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Balance per general ledger</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>468475</v>
+      </c>
+    </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
@@ -696,6 +729,132 @@
         <is>
           <t>per Bank of Canada 31 Dec close</t>
         </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Cheque #</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Payee</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Cleared date</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1041</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Northwind Traders</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>45779</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>2400</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Not yet cleared</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Contoso Ltd</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>46011</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>31500</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>46020</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1110</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Tailspin Toys</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>46021</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1111</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Adventure Works</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>46022</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>5375</v>
+      </c>
+      <c r="E21" s="7" t="n">
+        <v>46028</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="D22" s="6">
+        <f>SUM(D18:D21)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -804,7 +963,7 @@
         <f>SUM(B7:D7)</f>
         <v/>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="8">
         <f>E7/$E$12</f>
         <v/>
       </c>
@@ -828,7 +987,7 @@
         <f>SUM(B8:D8)</f>
         <v/>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="8">
         <f>E8/$E$12</f>
         <v/>
       </c>
@@ -851,7 +1010,7 @@
       <c r="E9" s="4" t="n">
         <v>14050</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="8">
         <f>E9/$E$12</f>
         <v/>
       </c>
@@ -875,7 +1034,7 @@
         <f>SUM(B10:D10)</f>
         <v/>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="8">
         <f>E10/$E$13</f>
         <v/>
       </c>
@@ -899,7 +1058,7 @@
         <f>SUM(B11:D11)</f>
         <v/>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="8">
         <f>E11/$E$12</f>
         <v/>
       </c>
@@ -1180,7 +1339,664 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Search for unrecorded liabilities, 31 Dec 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Purpose: test January payments and invoices for liabilities that belong in FY25</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Source: January cash disbursements journal and vendor invoices</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Prepared by: JS 06/10/2025</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Reviewed by:</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Invoice date</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Service date</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Payment date</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Recorded in AP?</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Conclusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Acme Plumbing</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>46034</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>46009</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>46042</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>18400</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Accrual needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Bolt Software</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>46027</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>46023</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>46031</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>FY26 expense, OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>City Power</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>46019</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>46006</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>46037</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>3200</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Investigate</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Delta Freight</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>46030</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>46044</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>12750</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Echo Legal</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>46025</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>46001</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>46047</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>9000</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>In AP listing</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Fresh Foods Co</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>46036</v>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>46032</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>46050</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>2150</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>FY26 expense, OK</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Revenue cut-off testing, 31 Dec 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Purpose: test sales either side of year-end are recorded in the right period</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Source: sales journal 20 Dec 2025 to 10 Jan 2026, shipping logs</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Prepared by: JS 06/10/2025</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Reviewed by:</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Invoice #</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Invoice date</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Ship date</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Conclusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>INV-880</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Adventure Works</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>46013</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>46012</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>INV-899</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Tailspin Toys</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>46020</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>46020</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>INV-901</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Northwind Traders</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>46022</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>46025</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>48000</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Shipped Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>INV-902</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Contoso Ltd</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>46024</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>46021</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>15500</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Shipped Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CN-14</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Fabrikam Inc</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>46028</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>46028</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>-9800</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Credit note</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>INV-910</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Wide World</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>46030</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>46029</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>7250</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>AR confirmations, 31 Dec 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Purpose: confirm significant customer balances directly with customers</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Source: AR aging at 31 Dec 2025, confirmation responses</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Prepared by: JS 06/10/2025</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Reviewed by:</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Balance per ledger</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Date sent</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Confirmed balance</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Explanation</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Alternative procedures</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Northwind Traders</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>23200</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>46032</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>23200</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Contoso Ltd</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>26050</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>46032</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>22750</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Fabrikam Inc</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>14050</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>46032</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Adventure Works</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>22250</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>46032</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Agreed to Jan receipts</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Tailspin Toys</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>17300</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1216,7 +2032,7 @@
           <t>B10</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>Total doesn't foot: adjusted balance excludes the last reconciling item</t>
         </is>
@@ -1233,7 +2049,7 @@
           <t>B13</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>Hard-coded FX rate, link to source</t>
         </is>
@@ -1246,7 +2062,7 @@
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>Please sign off and add the reviewer line</t>
         </is>
@@ -1263,7 +2079,7 @@
           <t>E9</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>Formula overwritten with a typed number, re-link the total</t>
         </is>
@@ -1276,7 +2092,7 @@
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>Discuss allowance methodology with manager</t>
         </is>
@@ -1289,7 +2105,7 @@
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>Where is the tickmark legend?</t>
         </is>
@@ -1306,9 +2122,35 @@
           <t>D8</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>Hard-coded useful life in depreciation formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>FY24 SURL</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Missing service dates on several items, so you can't conclude on the period</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FY24 Revenue cut-off</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Dec 31 invoice shipped in January was not identified</t>
         </is>
       </c>
     </row>
